--- a/Stats Sheet/Round Gaps/Translation.xlsx
+++ b/Stats Sheet/Round Gaps/Translation.xlsx
@@ -25,6 +25,9 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
     <x:t>_1mmortal_</x:t>
   </x:si>
   <x:si>
@@ -34,6 +37,9 @@
     <x:t>benidk</x:t>
   </x:si>
   <x:si>
+    <x:t>895</x:t>
+  </x:si>
+  <x:si>
     <x:t>Brodator</x:t>
   </x:si>
   <x:si>
@@ -140,6 +146,66 @@
   </x:si>
   <x:si>
     <x:t>ShyGus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>_Fost_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4EyedSlime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aalaan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ArcticSeagull</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bobbytheturtle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Broseph</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caydone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ChrisCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeJoshua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hecticity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JaeHasNoMaidens</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JustNolan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kelawesome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxEvasion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normoh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RqDix</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ryfri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ShootingGoats</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TalonBX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vetmire</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -498,10 +564,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G41"/>
+  <x:dimension ref="A1:H61"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7" s="1" customFormat="1">
+    <x:row r="1" spans="1:8" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>45203</x:v>
       </x:c>
@@ -511,16 +577,22 @@
       <x:c r="G1" s="1">
         <x:v>45307</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
+      <x:c r="H1" s="1">
+        <x:v>46131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
       <x:c r="F2" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="G2" s="0">
         <x:v>71</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
+      <x:c r="H2" s="0">
+        <x:v>824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -530,79 +602,91 @@
       <x:c r="G3" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
+      <x:c r="H3" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
@@ -611,18 +695,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -631,15 +715,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
@@ -648,44 +732,47 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -694,84 +781,93 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:8">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:8">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
@@ -780,21 +876,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:8">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -803,21 +899,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:8">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -826,38 +922,41 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:8">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:8">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
@@ -866,15 +965,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:8">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -883,58 +982,64 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:8">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:8">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:8">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>1</x:v>
@@ -943,18 +1048,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:8">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>1</x:v>
@@ -963,35 +1068,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:8">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:8">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>1</x:v>
@@ -1000,15 +1108,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:8">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>1</x:v>
@@ -1017,15 +1125,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:8">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>1</x:v>
@@ -1034,15 +1142,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:8">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>1</x:v>
@@ -1051,35 +1159,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:8">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:8">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>1</x:v>
@@ -1088,15 +1199,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:8">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>1</x:v>
@@ -1105,35 +1216,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:8">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:8">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>2</x:v>
@@ -1142,15 +1256,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:8">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>2</x:v>
@@ -1159,49 +1273,55 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:8">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:8">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:8">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>2</x:v>
@@ -1210,15 +1330,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:8">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>2</x:v>
@@ -1227,15 +1347,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:8">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>2</x:v>
@@ -1244,24 +1364,364 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:7">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:8">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D41" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:8">
+      <x:c r="A42" s="0">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:8">
+      <x:c r="A43" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D43" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:8">
+      <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D41" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="B44" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:8">
+      <x:c r="A45" s="0">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:8">
+      <x:c r="A46" s="0">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:8">
+      <x:c r="A47" s="0">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:8">
+      <x:c r="A48" s="0">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:8">
+      <x:c r="A49" s="0">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:8">
+      <x:c r="A50" s="0">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:8">
+      <x:c r="A51" s="0">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:8">
+      <x:c r="A52" s="0">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:8">
+      <x:c r="A53" s="0">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:8">
+      <x:c r="A54" s="0">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:8">
+      <x:c r="A55" s="0">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:8">
+      <x:c r="A56" s="0">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:8">
+      <x:c r="A57" s="0">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D57" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:8">
+      <x:c r="A58" s="0">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D58" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:8">
+      <x:c r="A59" s="0">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D59" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:8">
+      <x:c r="A60" s="0">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D60" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:8">
+      <x:c r="A61" s="0">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D61" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
